--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0100.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0100.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Aerial Energy</t>
+          <t>Năng Lượng Trên Không</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Không thể dọn dẹp môi trường khi đang ở Chế Độ Đồng Đội</t>
+          <t>Không thể dọn dẹp môi trường khi đang ở Chế Độ Hợp Tác.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Threat Elimination</t>
+          <t>Loại Bỏ Mối Đe Dọa</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Motorbike - Flight Track</t>
+          <t>Xe máy - Đường Bay</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Motorbike - Fixed Track</t>
+          <t>Xe máy - Đường ray cố định</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Motorbike - Stunt Track</t>
+          <t>Xe máy - Đường Đua Mạo Hiểm</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Light Builder</t>
+          <t>Thợ Xây Ánh Sáng</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Voidmatter Blocks</t>
+          <t>Khối Vật Chất Hư Không</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Ngày Hoàn Hảo Để Bay</t>
+          <t>Một Ngày Hoàn Hảo Để Bay Lượn</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Trái Tim Dimmr Vỡ Nát</t>
+          <t>Trái Tim Dimmr Vỡ</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Cuộc Gọi Từ Vượt Ngôi Sao</t>
+          <t>Tiếng Gọi Từ Vượt Ngôi Sao</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Endstate Matrix: Phần Thưởng Chu Kỳ Ngày Tận Thế</t>
+          <t>Ma Trận Tận Thế: Phần Thưởng Vòng Luân Hồi Ngày Tận Thế</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Bộ bao gồm</t>
+          <t>Bộ này bao gồm</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Ánh Sao Từ Những Ngày Qua" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Ánh Sao Từ Ngày Xưa" để mở khóa</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Auto Accepted</t>
+          <t>Đã chấp nhận tự động</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Đánh bại Mourning Aix lần đầu tiên</t>
+          <t>Hạ gục Mourning Aix lần đầu tiên</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Đánh bại Feilian Beringal lần đầu tiên</t>
+          <t>Lần đầu đánh bại Feilian Beringal</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Đánh bại Lampylumen Myriad lần đầu tiên</t>
+          <t>Lần đầu đánh bại Lampylumen Myriad</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Đánh bại Crownless lần đầu tiên</t>
+          <t>Lần đầu đánh bại Crownless</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Đánh bại Bell-Borne Geochelone lần đầu tiên</t>
+          <t>Đánh bại Rùa Địa Chấn Bell-Borne lần đầu tiên</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Đánh bại Thundering Mephis lần đầu tiên</t>
+          <t>Hạ gục Thundering Mephis lần đầu tiên</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Đánh bại Bell-Borne Geochelone 50 lần</t>
+          <t>Đánh bại Rùa Địa Chấn Bell-Borne 50 lần</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Đánh bại Mourning Aix 50 lần</t>
+          <t>Hạ gục Mourning Aix 50 lần</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Đánh bại Lampylumen Myriad 50 lần</t>
+          <t>Hạ gục Lampylumen Myriad 50 lần.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Đánh bại Tempest Mephis 50 lần</t>
+          <t>Hạ gục Tempest Mephis 50 lần</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Thực hiện né tránh tổng cộng 50 lần</t>
+          <t>Tổng cộng né tránh thành công 50 lần</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Thực hiện Tấn Công Phản Đòn 10 lần tổng cộng</t>
+          <t>Phòng thủ thành công 10 lần.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Dùng Levitator nâng vũ khí của Inferno Rider và tấn công Inferno Rider bằng nó</t>
+          <t>Dùng Levitator nâng vũ khí của Inferno Rider lên và tấn công hắn bằng chính nó</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Sử dụng kỹ năng Echo loại biến hình ít nhất 10 lần</t>
+          <t>Kích hoạt kỹ năng Echo loại biến hình ít nhất 10 lần</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Đánh bại 20 Howler</t>
+          <t>Tiêu diệt 20 Howler</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Đánh bại Havoc Dreadmanes 10 lần bằng Fusion Dreadmane</t>
+          <t>Tiêu diệt Havoc Dreadmanes 10 lần bằng Fusion Dreadmane.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Đánh bại 100 Exile</t>
+          <t>Hạ gục 100 Exile</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Đánh bại 66 Snip Snaps bằng Resonator sử dụng Gauntlets</t>
+          <t>Tiêu diệt 66 Snip Snap bằng Resonator Găng tay</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Đánh bại 66 Snip Snaps bằng Resonator sử dụng Pistols</t>
+          <t>Tiêu diệt 66 Snip Snap bằng Resonator Súng</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Đánh bại 66 Snip Snaps bằng Resonator sử dụng Kiếm</t>
+          <t>Tiêu diệt 66 Snip Snap bằng Resonator Kiếm đơn</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Đánh bại 66 Snip Snaps bằng Resonator sử dụng Broadblade</t>
+          <t>Tiêu diệt 66 Snip Snap bằng Resonator Đại kiếm</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Đánh bại 66 Tick Tacks bằng Resonator sử dụng Rectifier</t>
+          <t>Tiêu diệt 66 Tick Tack bằng Resonator Pháp khí</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Bị hạ gục một lần bởi đòn tự hủy của cậu bé</t>
+          <t>Bị cậu bé tự sát tấn công một lần</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Bị hạ gục một lần bởi Excarat</t>
+          <t>Bị hạ gục bởi một Excarat</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Bị hạ gục một lần bởi đòn tấn công lao tới của Inferno Rider</t>
+          <t>Bị hạ gục bởi đòn tấn công lao thẳng của Inferno Rider</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Bị hạ gục bởi trò tung hứng của Gulpuff</t>
+          <t>Bị Gulpuff chơi trò tung hứng đến chết</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 30</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 30</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 30</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 30</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 35</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 35</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Mức độ khó này chưa khả dụng</t>
+          <t>Mức độ khó này vẫn chưa mở khóa.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Nhận 1.200 Trial Coin</t>
+          <t>Thu thập 1.200 Đồng Xu Thử Nghiệm</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 1.000 Data Sets</t>
+          <t>Thu thập tổng cộng 1.000 Bộ Dữ Liệu</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 2.500 Data Sets</t>
+          <t>Thu thập tổng cộng 2.500 Bộ Dữ Liệu</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 3.500 Data Sets</t>
+          <t>Thu thập tổng cộng 3.500 Bộ Dữ Liệu.</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Nhận 1.200 Hazard Record</t>
+          <t>Thu thập 1.200 Bản Ghi Nguy Hiểm</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 10 hoặc hoàn thành Act 3 để mở khóa Milestones</t>
+          <t>Đạt Cấp Độ Liên Minh 10 hoặc hoàn thành Chương 3 để mở khóa Cột Mốc</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 2000 Sacred Muối</t>
+          <t>Thu thập tổng cộng 2.000 Muối Thánh</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 1.000 Sacred Muối</t>
+          <t>Thu thập tổng cộng 1.000 Muối Thánh</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 4.000 Modules</t>
+          <t>Thu thập tổng cộng 4.000 Mô-đun</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 8.000 Modules</t>
+          <t>Thu thập tổng cộng 8.000 Mô-đun</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và hoàn thành cuộc săn đầu tiên trong Nhiệm Vụ Chính "By Sun's Burning Hand"</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành cuộc săn đầu tiên trong Nhiệm Vụ Chính "Dưới Bàn Tay Thiêu Đốt Của Mặt Trời"</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Đạt Duelist Level 2</t>
+          <t>Đạt Cấp Đấu Thủ 2</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Đạt Duelist Level 4</t>
+          <t>Đạt Cấp Đấu Thủ 4</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Đạt Duelist Level 6</t>
+          <t>Đạt Cấp Độ Đấu Thủ 6</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Đạt Duelist Level 8</t>
+          <t>Đạt Cấp Độ Đấu Thủ 8</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Đạt Duelist Level 10</t>
+          <t>Đạt Cấp Đấu Thủ 10</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Đạt Duelist Level 12</t>
+          <t>Đạt Cấp Đấu Thủ 12</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Đạt Duelist Level 3</t>
+          <t>Đạt Cấp Đấu Thủ 3</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Thu thập 500 Tokens of Radiance</t>
+          <t>Thu thập 500 Mảnh Ánh Sáng</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Thu thập 800 Tokens of Radiance</t>
+          <t>Thu thập 800 Mảnh Ánh Sáng.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Sử dụng tổng cộng 1.000 Abyssal Corals</t>
+          <t>Dùng tổng cộng 1.000 Abyssal Corals</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Đến Helm Village trong nhiệm vụ để mở khóa</t>
+          <t>Đến Làng Helm trong nhiệm vụ mở khóa</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Có sẵn sau khi mở khóa Advanced Hull</t>
+          <t>Mở sau khi mở khóa Nâng Cấp Thân Tàu Cao Cấp</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Có sẵn thông qua tiến trình nhiệm vụ và mở khóa Abyssal Hull</t>
+          <t>Mở khóa thông qua tiến trình nhiệm vụ và kích hoạt Abyssal Hull</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Có sẵn thông qua tiến trình nhiệm vụ và mở khóa Oceanic Hull</t>
+          <t>Mở khóa thông qua tiến trình nhiệm vụ và kích hoạt Oceanic Hull</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Có sẵn sau khi mở khóa tất cả Kỹ Năng Câu Cá</t>
+          <t>Mở sau khi mở khóa tất cả Kỹ Năng Câu Cá</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Có sẵn sau khi mở khóa tất cả Kỹ Năng Câu Cá</t>
+          <t>Mở sau khi mở khóa tất cả Kỹ Năng Câu Cá</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Có sẵn sau khi mở khóa tất cả Kỹ Năng Câu Cá</t>
+          <t>Mở sau khi mở khóa tất cả Kỹ Năng Câu Cá</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Thu thập 800 Monnaies để mở khóa</t>
+          <t>Thu thập 800 Monnaies để mở khóa.</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Sử dụng tổng cộng 500 Resonant Calcites</t>
+          <t>Sử dụng tổng cộng 500 Resonant Calcite.</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Sử dụng tổng cộng 2.000 Resonant Calcites</t>
+          <t>Dùng tổng cộng 2.000 Resonant Calcites</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Complete Phantasm Amass II</t>
+          <t>Hoàn thành Tích Lũy Ảo Ảnh II</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Complete Phantasm Amass III</t>
+          <t>Hoàn thành Tích Lũy Ảo Ảnh III</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Hoàn thành Phantasm Amass IV: Dream of Desperation</t>
+          <t>Hoàn thành Phantasm Amass IV: Giấc Mộng Tuyệt Vọng</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Hoàn thành Phantasm Amass V: Dream of Confusion</t>
+          <t>Hoàn thành Phantasm Amass V: Giấc Mộng Mê Lòng</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Giải cứu con mèo trắng đã trốn thoát qua cánh cổng</t>
+          <t>Bắt con mèo trắng đã chạy qua cổng</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Hoàn thành "When the Night Knocks"</t>
+          <t>Hoàn thành "Khi Bóng Đêm Gõ Cửa".</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Nhận 400 Mảnh Giấc mơ</t>
+          <t>Thu thập 400 Mảnh Giấc Mơ.</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Nhận 800 Mảnh Giấc mơ</t>
+          <t>Thu thập 800 Mảnh Giấc Mơ Nhỏ.</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Nhận 1.200 Mảnh Giấc mơ</t>
+          <t>Thu thập 1.200 Mảnh Giấc Mơ Nhỏ.</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Hoàn thành Dreamscape Odyssey: Against Tất cả Odds</t>
+          <t>Hoàn thành Hành Trình Giấc Mơ: Vượt Qua Mọi Gian Nan</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Hoàn thành Dreamscape Odyssey: The Mountain and Six Credits</t>
+          <t>Hoàn thành Hành Trình Giấc Mơ: Ngọn Núi và Sáu Đồng Tín Dụng</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Hoàn thành Dreamscape Odyssey: Little Warrior's Stage</t>
+          <t>Hoàn thành Hành Trình Giấc Mơ: Sân Khấu Của Chiến Binh Nhí</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Complete Dreamscape Odyssey: Neverending Inferno</t>
+          <t>Hoàn thành Hành Trình Giấc Mơ: Hỏa Ngục Bất Tận</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Hoàn thành Dreamscape Odyssey: A Study in Snow</t>
+          <t>Hoàn thành Hành Trình Giấc Mơ: Nghiên Cứu Tuyết Rơi</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Complete Dreamscape Odyssey: Blooming Reverie</t>
+          <t>Hoàn thành Hành Trình Giấc Mơ: Khúc Hoài Niệm Nở Hoa</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Complete Rift Runner I</t>
+          <t>Hoàn thành Rift Runner I</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Complete Rift Runner II</t>
+          <t>Hoàn thành Rift Runner II</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Complete Rift Runner III</t>
+          <t>Hoàn thành Rift Runner III</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Complete Rift Runner IV</t>
+          <t>Hoàn thành Rift Runner IV</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Complete Rift Runner V</t>
+          <t>Hoàn thành Rift Runner V</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Complete Rift Runner VI</t>
+          <t>Hoàn thành Rift Runner VI</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Complete Rift Runner VII</t>
+          <t>Hoàn thành Rift Runner VII</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Hoàn thành Nightmare Revisits với 2 Resonator chính khác nhau</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện với 2 Resonator chính khác nhau</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Hoàn thành Nightmare Revisits với 4 Resonator chính khác nhau</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện với 4 Resonator chính khác nhau</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Hoàn thành Nightmare Revisits với 6 Resonator chính khác nhau</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện với 6 Resonator chính khác nhau</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Hoàn thành "Carnival in Slumberland Ⅱ"</t>
+          <t>Hoàn thành "Lễ Hội Giấc Mơ Ⅱ"</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Hoàn thành "Carnival in Slumberland Ⅲ"</t>
+          <t>Hoàn thành "Lễ Hội Giấc Mơ Ⅲ"</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Hoàn thành "Carnival in Slumberland Ⅳ"</t>
+          <t>Hoàn thành "Lễ Hội Giấc Mơ Ⅳ"</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Chơi Carnival in Slumberland VI: Chaos một lần</t>
+          <t>Phát Carnival in Slumberland VI: Chaos một lần</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Tiến hành nhiệm vụ để mở khóa</t>
+          <t>Tiếp tục nhiệm vụ để mở khóa</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Hoàn thành yêu cầu điều kiện tiên quyết để mở khóa</t>
+          <t>Hoàn thành yêu cầu tiên quyết để mở khóa</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Hoàn thành yêu cầu điều kiện tiên quyết để mở khóa</t>
+          <t>Hoàn thành yêu cầu tiên quyết để mở khóa</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Hoàn thành yêu cầu điều kiện tiên quyết để mở khóa</t>
+          <t>Hoàn thành yêu cầu tiên quyết để mở khóa</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Hoàn thành yêu cầu điều kiện tiên quyết để mở khóa</t>
+          <t>Hoàn thành yêu cầu tiên quyết để mở khóa</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Kiểm tra xem chức năng Tacet Field đã được kích hoạt chưa</t>
+          <t>Kiểm tra xem chức năng Tổ Tacet đã kích hoạt chưa</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Kiểm tra xem chức năng trực tuyến đã được kích hoạt chưa</t>
+          <t>Kiểm tra xem chức năng trực tuyến đã kích hoạt chưa</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Kiểm tra xem chức năng Tower of Adversity đã được kích hoạt chưa</t>
+          <t>Kiểm tra xem chức năng Tháp Nghịch Cảnh đã kích hoạt chưa</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Kiểm tra xem Tower of Adversity đã được kích hoạt chưa</t>
+          <t>Kiểm tra xem Tháp Nghịch Cảnh đã kích hoạt chưa</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Kiểm tra xem Chaotic Sound Flow đã được kích hoạt chưa</t>
+          <t>Kiểm tra xem Luồng Âm Thanh Hỗn Loạn đã kích hoạt chưa</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Kiểm tra xem nhiệm vụ Pioneer Association đã được kích hoạt chưa</t>
+          <t>Kiểm tra xem nhiệm vụ Hiệp Hội Tiên Phong đã kích hoạt chưa</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ Dim Forest</t>
+          <t>Hoàn thành Nhiệm Vụ Rừng Mờ</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ Whining Aix's Mire - Mourning Aix</t>
+          <t>Hoàn thành Nhiệm Vụ Whining Aix's Mire - Mourning Aix</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách Inferno Rider</t>
+          <t>Hoàn thành Thử Thách Kỵ Sĩ Hỏa Ngục</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Nhận được 1 Flour</t>
+          <t>Lấy 1 Bột Mì</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Nhận được 1 Cooking Oil</t>
+          <t>Lấy 1 Dầu Ăn</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và hoàn thành Chương II Prologue để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Lời Mở Đầu Chương II để mở khóa</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 20</t>
+          <t>Đạt Cấp Độ Liên Minh 20</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 35 và đến Bell Tower trong nhiệm vụ chính "Flames of Heart"</t>
+          <t>Đạt Cấp Độ Liên Minh 35 và đến Tháp Chuông trong Nhiệm vụ Chính "Flames of Heart"</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai đoạn 1 để mở khóa</t>
+          <t>Hoàn thành Giai Đoạn 1 để mở khóa</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai đoạn 2 để mở khóa</t>
+          <t>Hoàn thành Giai Đoạn 2 để mở khóa</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai đoạn 3 để mở khóa</t>
+          <t>Hoàn thành Giai Đoạn 3 để mở khóa</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai đoạn 4 để mở khóa</t>
+          <t>Hoàn thành Giai Đoạn 4 để mở khóa</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai đoạn 5 để mở khóa</t>
+          <t>Hoàn thành Giai Đoạn 5 để mở khóa</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai đoạn 6 để mở khóa</t>
+          <t>Hoàn thành Giai Đoạn 6 để mở khóa</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai đoạn 7 để mở khóa</t>
+          <t>Hoàn thành Giai Đoạn 7 để mở khóa</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Mở khóa 18 Mục trong Bộ sưu tập</t>
+          <t>Mở khóa 18 Vật Phẩm trong Thư Viện</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Mở khóa 36 Mục trong Bộ sưu tập</t>
+          <t>Mở khóa 36 Vật Phẩm trong Phòng Trưng Bày</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Mở khóa 54 Mục trong Bộ sưu tập</t>
+          <t>Mở khóa 54 Vật phẩm trong Bộ Sưu Tập</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Mở khóa 2 Vũ khí trong Bộ sưu tập</t>
+          <t>Mở khóa 2 Vũ Khí trong Thư Viện</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Mở khóa 4 Vũ khí trong Bộ sưu tập</t>
+          <t>Mở khóa 4 Vũ Khí trong Bộ Sưu Tập</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Mở khóa 8 Vũ khí trong Bộ sưu tập</t>
+          <t>Mở khóa 8 Vũ Khí trong Bộ Sưu Tập</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Tiến hóa 2 vũ khí thành Dạng Tối thượng</t>
+          <t>Tiến hóa 2 vũ khí thành Hình Thái Tối Thượng</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Tiến hóa 4 vũ khí thành Dạng Tối thượng</t>
+          <t>Nâng cấp 4 vũ khí lên Hình Thái Tối Thượng</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Tiến hóa 6 vũ khí thành Dạng Tối thượng</t>
+          <t>Nâng cấp 6 vũ khí lên Hình Thái Tối Thượng</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 5</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 5</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 6</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 6</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 7</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 7</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 8</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 8</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 9</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 9</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 10</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 10</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 11</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 11</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 13</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 13</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 15</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 15</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 16</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 16</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 18</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 18</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 20</t>
+          <t>Mở khóa ở Cấp Liên Minh 20</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 21</t>
+          <t>Mở khóa ở Cấp Liên Minh 21</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 22</t>
+          <t>Mở khóa ở Cấp Liên Minh 22</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 23</t>
+          <t>Mở khóa ở Cấp Liên Minh 23</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 30</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 30</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 9 &amp; mở khóa Cửa Hàng</t>
+          <t>Đạt Cấp Liên Minh 9 &amp; mở khóa Cửa Hàng.</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính: "Đến Bờ Biển Cuối Cùng" và Nhiệm Vụ Phụ "Vảy Quá Khứ" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Tới Bờ Cát Cuối Cùng" và Nhiệm Vụ Phụ "Vảy Quá Khứ" để mở khóa</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính Chương I Hồi VIII "Đến Bờ Biển Cuối Cùng" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính Chương I Hồi VIII "Tới Bờ Cát Cuối Cùng" để mở khóa</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính Chương II Hồi III và Nhiệm Vụ Phụ "Vảy Quá Khứ" để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi III và Nhiệm Vụ Phụ "Thang Đo Quá Khứ" của Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Nhận được 600 Tinh Thể Ma Trận để mở khóa</t>
+          <t>Thu thập 600 Tinh Thể Ma Trận để mở khóa</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Nhận được 1.200 Tinh Thể Ma Trận để mở khóa</t>
+          <t>Thu thập 1.200 Tinh Thể Ma Trận để mở khóa</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Nhận được 1.500 Tinh Thể Ma Trận để mở khóa</t>
+          <t>Thu thập 1.500 Tinh Thể Ma Trận để mở khóa</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính Chương II Hồi V "Bóng Tối Vinh Quang" để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi V "Bóng Tối Của Vinh Quang" của Nhiệm Vụ Chính để Mở Khóa</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính Chương II Hồi V và Nhiệm Vụ Phụ "Vảy Quá Khứ" để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi V và Nhiệm Vụ Phụ "Thang Đo Quá Khứ" của Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính Chương II Hồi VII "Những Kẻ Bắt Giấc Mơ Trong Vườn Bí Mật" để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi VII "Những Giấc Mộng Trong Vườn Bí Mật" trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính Chương II Hồi VII và Nhiệm Vụ Phụ "Vảy Quá Khứ" để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi VII trong Nhiệm Vụ Chính và Nhiệm Vụ Phụ "Thang Đo Quá Khứ" để mở khóa</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính Chương II Hồi VIII "Dưới Bàn Tay Thiêu Đốt Của Mặt Trời" để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi VIII "Dưới Bàn Tay Thiêu Đốt Của Mặt Trời" trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính Chương II Hồi VIII và Nhiệm Vụ Phụ "Vảy Quá Khứ" để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi VIII trong Nhiệm Vụ Chính và Nhiệm Vụ Phụ "Thang Đo Quá Khứ" để mở khóa</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính Chương III Hồi I "Điều Cháy Bên Dưới Vùng Đất Băng Giá" để mở khóa</t>
+          <t>Hoàn thành Chương III Hồi I "Điều Gì Cháy Bên Dưới Băng Giá" trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Hoàn thành cấp độ khó II</t>
+          <t>Hoàn thành cấp độ Khó II</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Hoàn thành cấp độ khó III</t>
+          <t>Hoàn thành cấp độ Khó III</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Đạt SOL3 Giai Đoạn 1</t>
+          <t>Đạt Giai Đoạn 1 SOL3</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Đạt SOL3 Giai Đoạn 2</t>
+          <t>Đạt Giai Đoạn 2 SOL3</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Đạt SOL3 Giai đoạn 3</t>
+          <t>Đạt Giai Đoạn 3 SOL3</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Đạt SOL3 Giai đoạn 4</t>
+          <t>Đạt Giai Đoạn 4 SOL3</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Đạt SOL3 Giai đoạn 5</t>
+          <t>Đạt Giai Đoạn 5 SOL3</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 3</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 3</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 10</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 10</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Có thể nâng cấp ở Hạng Thăng Tinh Resonator 1</t>
+          <t>Nâng cấp được khi Resonator đạt Cấp Thăng Hoa 1</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Có thể nâng cấp ở Hạng Thăng Tinh Resonator 2</t>
+          <t>Nâng cấp được khi Resonator đạt Cấp Thăng Hoa 2</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Có thể nâng cấp ở Hạng Thăng Tinh Resonator 3</t>
+          <t>Nâng cấp được khi Resonator đạt Cấp Thăng Hoa 3</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Có thể nâng cấp ở Hạng Thăng Tinh Resonator 4</t>
+          <t>Nâng cấp được khi Resonator đạt Cấp Thăng Hoa 4</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Có thể nâng cấp ở Hạng Thăng Tinh Resonator 5</t>
+          <t>Nâng cấp được khi Resonator đạt Cấp Thăng Hoa 5</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Có thể nâng cấp ở Hạng Thăng Tinh Resonator 6</t>
+          <t>Nâng cấp được khi Resonator đạt Cấp Thăng Hoa 6</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Có thể nâng cấp ở Hạng Thăng Tinh Resonator 7</t>
+          <t>Nâng cấp được khi Resonator đạt Cấp Thăng Hoa 7</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 7</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 7</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 6</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 6</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 8</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 8</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 10</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 10</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 12</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 12</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 14</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Mở khóa ở Hạng Thăng Tinh Resonator 1</t>
+          <t>Mở khóa ở Hạng Thăng Hoa Resonator 1</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Mở khóa ở Hạng Thăng Tinh Resonator 4</t>
+          <t>Mở khóa ở Hạng Thăng Hoa Resonator 4</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 17</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 17</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 99</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 99</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 15</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 15</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 30</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 30</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 35</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 35</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 40</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 40</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 45</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 45</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 50</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 50</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 55</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 55</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Thăng cấp tiếp theo ở Giai đoạn SOL3 1</t>
+          <t>Tiến Hóa Tiếp Theo ở Giai Đoạn SOL3-1</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Thăng cấp tiếp theo ở Giai đoạn SOL3 2</t>
+          <t>Tiến Hóa Tiếp Theo ở Giai Đoạn SOL3-2</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Thăng cấp tiếp theo ở Giai đoạn SOL3 3</t>
+          <t>Tiến Hóa Tiếp Theo ở Giai Đoạn SOL3-3</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Thăng cấp tiếp theo ở Giai đoạn SOL3 4</t>
+          <t>Tiến Hóa Tiếp Theo ở Giai Đoạn SOL3-4</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Thăng cấp tiếp theo ở Giai đoạn SOL3 5</t>
+          <t>Tiến Hóa Tiếp Theo ở Giai Đoạn SOL3-5</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Thăng cấp tiếp theo ở Giai đoạn SOL3 6</t>
+          <t>Tiến Hóa Tiếp Theo ở Giai Đoạn SOL3-6</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Thăng cấp tiếp theo ở Giai đoạn SOL3 7</t>
+          <t>Thăng cấp tiếp theo ở Giai Đoạn SOL3 7</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Thăng cấp tiếp theo ở Giai đoạn SOL3 8</t>
+          <t>Thăng cấp tiếp theo ở Giai Đoạn SOL3 8</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Thăng cấp tiếp theo ở Giai đoạn SOL3 9</t>
+          <t>Thăng cấp tiếp theo ở Giai Đoạn SOL3 9</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Thăng cấp tiếp theo ở Giai đoạn SOL3 10</t>
+          <t>Tiến Hóa Tiếp Theo ở Giai Đoạn SOL3-10</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 10</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 10</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 30</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 30</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 40</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 40</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 50</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 50</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 60</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 60</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 65</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 65</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 70</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 70</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Hoàn thành Đột Phá Cấp Độ Liên Minh trong Sonoro Sphere</t>
+          <t>Hoàn thành Đột Phá Cấp Độ Liên Minh tại Sonoro Sphere</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Tacetite Highlands</t>
+          <t>Cao Nguyên Tacetite</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Tacetite Highlands</t>
+          <t>Cao Nguyên Tacetite</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Lampy Cat hoàn thành 1</t>
+          <t>Mèo Đèn Hoàn Thành 1</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Lampy Cat hoàn thành 2</t>
+          <t>Mèo Đèn Hoàn Thành 2</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Lampy Cat hoàn thành 3</t>
+          <t>Mèo Đèn Hoàn Thành 3</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Lampy Cat hoàn thành 4</t>
+          <t>Mèo Đèn Hoàn Thành 4</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Central Plains West</t>
+          <t>Central Plains Phía Tây</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Central Plains West</t>
+          <t>Central Plains Phía Tây</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Central Plains West</t>
+          <t>Central Plains Phía Tây</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Central Plains West</t>
+          <t>Central Plains Phía Tây</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Thông báo mở khóa - Jinzhou - Nhỏ - Dragon's Residence</t>
+          <t>Thông Báo Mở Khóa - Jinzhou - Nhỏ - Dinh Thự Rồng</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Thông báo mở khóa - Jinzhou - Nhỏ - Industrial Area</t>
+          <t>Thông Báo Mở Khóa - Jinzhou - Nhỏ - Khu Công Nghiệp</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Chưa mở khóa - Jinzhou - Nhỏ - Dragon's Residence</t>
+          <t>Chưa mở khóa - Jinzhou - Khu nhỏ - Dinh Thự Rồng</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Chưa mở khóa - Jinzhou - Nhỏ - Industrial Area</t>
+          <t>Chưa mở khóa - Jinzhou - Khu nhỏ - Khu Công Nghiệp</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Jinzhou Mainline Step Completion Status 4</t>
+          <t>Tiến Độ Hoàn Thành Bước Chính Tuyến Jinzhou 4</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Tàn Tích phá hủy Tacetite Mở khóa Rương Cung Ứng 1</t>
+          <t>Tàn Tích Phá Hủy Tacetite - Rương Vật Tư 1 Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Instance 3002 Step 1 Completed</t>
+          <t>Giai đoạn 1 - Tổ Tacet 3002 hoàn thành</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Instance 3002 Step 2 Completed</t>
+          <t>Giai đoạn 2 - Tổ Tacet 3002 hoàn thành</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Instance 3002 Step 3 Completed</t>
+          <t>Giai đoạn 3 - Tổ Tacet 3002 hoàn thành</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Instance 3002 Step 4 Completed</t>
+          <t>Giai đoạn 4 Hoàn thành - Thử thách 3002</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Instance 3002 Step 5 Completed</t>
+          <t>Giai đoạn 5 Hoàn thành - Thử thách 3002</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Instance 3002 Step 6 Completed</t>
+          <t>Giai đoạn 6 Hoàn thành - Thử thách 3002</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Phó Bản 3002 Tiêu diệt đợt quái vật đầu tiên</t>
+          <t>Đợt quái vật đầu tiên - Tổ Tacet 3002 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Phó Bản 3002 Tiêu diệt đợt quái vật thứ hai</t>
+          <t>Đợt quái vật thứ hai - Tổ Tacet 3002 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Phó Bản 3002 Tiêu diệt đợt quái vật thứ hai</t>
+          <t>Đợt quái vật thứ hai - Tổ Tacet 3002 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Phó Bản 3002 Phần thưởng kinh nghiệm Rương Cung Ứng</t>
+          <t>Phần thưởng Kinh nghiệm Rương Cung cấp - Thử thách 3002</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Instance 4000 Completed</t>
+          <t>Hoàn thành Thử thách 4000</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Kiểm tra STA đủ 20</t>
+          <t>Kiểm tra xem Thể Lực còn đủ 20 không</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Kiểm tra nút Chuyển có nhãn Sẵn Sàng</t>
+          <t>Kiểm tra xem nhãn "Sẵn Sàng" của chuyển đổi đã bật chưa</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Protected Entity Dead</t>
+          <t>Đối tượng được bảo vệ đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Instance Switch Interaction Completed</t>
+          <t>Hoàn thành tương tác chuyển đổi Thể Hiện</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Jinzhou Temporary Instance Entrance Unlocked</t>
+          <t>Lối vào Phiên Bản Tạm Tấn Châu đã mở khóa</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Thông báo mở khóa - Lối vào Phó Bản Tạm thời Jinzhou</t>
+          <t>Thông Báo Mở Khóa - Lối Vào Phiên Bản Tạm Thời Jinzhou</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Teleport Unlocked - Chip Instance</t>
+          <t>Đã mở khóa Dịch Chuyển - Bản Thể Chip</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Notification Unlocked - Chip Instance</t>
+          <t>Thông Báo Mở Khóa - Phiên Bản Chip</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Teleport Unlocked - Weapon Instance</t>
+          <t>Đã mở khóa Dịch Chuyển - Bản Thể Vũ Khí</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Notification Unlocked - Weapon Instance</t>
+          <t>Thông Báo Mở Khóa - Phiên Bản Vũ Khí</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Teleport Unlocked - Character Instance</t>
+          <t>Đã mở khóa Dịch Chuyển - Bản Thể Nhân Vật</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Notification Unlocked - Character Instance</t>
+          <t>Thông Báo Mở Khóa - Phiên Bản Nhân Vật</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Thông báo mở khóa - Phó Bản Thử Thách</t>
+          <t>Thông Báo Mở Khóa - Phiên Bản Thử Thách</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Lối vào Phụ Bản Tạm Thời Jinzhou Chưa Mở Khóa</t>
+          <t>Lối vào Phiên Bản Tạm Tấn Châu chưa mở khóa</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Teleport Not Unlocked - Chip Instance</t>
+          <t>Chưa mở khóa - Thể Chip</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Teleport Not Unlocked - Weapon Instance</t>
+          <t>Chưa mở khóa - Thể Vũ Khí</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Teleport Not Unlocked - Character Instance</t>
+          <t>Chưa mở khóa - Thể Nhân Vật</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Teleport Not Unlocked - Character Instance</t>
+          <t>Chưa mở khóa - Thể Nhân Vật</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Instance 4000 Step 1 Completed</t>
+          <t>Giai đoạn 1 Hoàn thành - Thử thách 4000</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Instance 4000 Step 2 Completed</t>
+          <t>Giai đoạn 2 Hoàn thành - Thử thách 4000</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Instance 4000 Step 3 Completed</t>
+          <t>Giai đoạn 3 Hoàn thành - Thử thách 4000</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Instance 4000 Step 4 Completed</t>
+          <t>Giai đoạn 4 Hoạt động 4000 hoàn tất</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Instance 4000 Step 5 Completed</t>
+          <t>Giai đoạn 5 Hoạt động 4000 hoàn tất</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Instance 4000 Step 6 Completed</t>
+          <t>Giai đoạn 6 Hoạt động 4000 hoàn tất</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Nhất Phụ Bản 4000</t>
+          <t>Đợt quái vật thứ nhất bị tiêu diệt - Thử thách 4000</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Hai Phụ Bản 4000</t>
+          <t>Đợt quái vật thứ hai bị tiêu diệt - Thử thách 4000</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Hai Phụ Bản 4000</t>
+          <t>Đợt quái vật thứ hai bị tiêu diệt - Thử thách 4000</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Mở Rương Vật Phẩm Phụ Bản 4000</t>
+          <t>Rương tiếp tế Hoạt động 4000 đã mở</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Kiểm tra Số lượng Vật phẩm Phụ Bản 4000</t>
+          <t>Kiểm tra số lượng vật phẩm - Thử thách 4000</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Instance 4000 Exit Interaction</t>
+          <t>Tương tác thoát - Thử thách 4000</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Instance 4500 Step 1 Completed</t>
+          <t>Bước 1 của Thể Hiện 4500 hoàn thành</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Instance 4500 Step 2 Completed</t>
+          <t>Bước 2 của Thể Hiện 4500 hoàn thành</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Instance 4500 Step 3 Completed</t>
+          <t>Bước 3 của Thể Hiện 4500 hoàn thành</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Instance 4500 Step 4 Completed</t>
+          <t>Bước 4 của Thể Hiện 4500 hoàn thành</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Instance 4500 Step 5 Completed</t>
+          <t>Bước 5 của Thể Hiện 4500 hoàn thành</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Instance 4500 Step 6 Completed</t>
+          <t>Bước 6 của Thể Hiện 4500 hoàn thành</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Nhất Phụ Bản 4500</t>
+          <t>Đợt quái vật đầu tiên của Thể Hiện 4500 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Hai Phụ Bản 4500</t>
+          <t>Đợt quái vật thứ hai của Thể Hiện 4500 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Hai Phụ Bản 4500</t>
+          <t>Đợt quái vật thứ hai của Thể Hiện 4500 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Mở Rương Vật Phẩm Phụ Bản 4500</t>
+          <t>Mở Rương Cung Cấp Thể Hiện 4500</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Nhận Thưởng Kinh Nghiệm Rương Vật Phẩm Phụ Bản 4500</t>
+          <t>Phần thưởng Kinh nghiệm Rương Cung Cấp Thể Hiện 4500</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Protected Entity Dead</t>
+          <t>Đối tượng được bảo vệ đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Instance 4500 Exit Interaction</t>
+          <t>Tương tác thoát khỏi Thể Hiện 4500</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Instance 5000 Step 1 Completed</t>
+          <t>Bước 1 của Thể Hiện 5000 hoàn thành</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Instance 5000 Step 2 Completed</t>
+          <t>Bước 2 của Thể Hiện 5000 hoàn thành</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Instance 5000 Step 3 Completed</t>
+          <t>Bước 3 của Thể Hiện 5000 hoàn thành</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Instance 5000 Step 4 Completed</t>
+          <t>Bước 4 của Thể Hiện 5000 hoàn thành</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Instance 5000 Step 5 Completed</t>
+          <t>Bước 5 của Thể Hiện 5000 hoàn thành</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Instance 5000 Step 6 Completed</t>
+          <t>Bước 6 của Thể Hiện 5000 hoàn thành</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Nhất Phụ Bản 5000</t>
+          <t>Đợt quái vật đầu tiên của Thể Hiện 5000 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Hai Phụ Bản 5000</t>
+          <t>Đợt quái vật thứ hai của Thể Hiện 5000 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Hai Phụ Bản 5000</t>
+          <t>Đợt quái vật thứ hai của Thể Hiện 5000 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Mở Rương Vật Phẩm Phụ Bản 4500</t>
+          <t>Mở Rương Cung Cấp Thể Hiện 4500</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Nhận Thưởng Kinh Nghiệm Rương Vật Phẩm Phụ Bản 5000</t>
+          <t>Rương vật tư Thể Hiện 5000 - Phần thưởng Kinh nghiệm</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Kiểm tra Số lượng Vật phẩm Phụ Bản 5000</t>
+          <t>Kiểm tra số lượng vật phẩm trong Thể Hiện 5000</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Instance 5000 Exit Interaction</t>
+          <t>Tương tác thoát khỏi Thể Hiện 5000</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Instance 4010 Step 1 Completed</t>
+          <t>Giai đoạn 1 Hoạt động 4010 hoàn tất</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Instance 4010 Step 2 Completed</t>
+          <t>Giai đoạn 2 Hoạt động 4010 hoàn tất</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Instance 4010 Step 3 Completed</t>
+          <t>Giai đoạn 3 Hoạt động 4010 hoàn tất</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Instance 4010 Step 4 Completed</t>
+          <t>Giai đoạn 4 Hoạt động 4010 hoàn tất</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Instance 4010 Step 5 Completed</t>
+          <t>Giai đoạn 5 Hoạt động 4010 hoàn tất</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Instance 4010 Step 6 Completed</t>
+          <t>Giai đoạn 6 Hoạt động 4010 hoàn tất</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Nhất Phụ Bản 4010</t>
+          <t>Đợt quái vật đầu Hoạt động 4010 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Hai Phụ Bản 4010</t>
+          <t>Đợt quái vật thứ hai Hoạt động 4010 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Hai Phụ Bản 4010</t>
+          <t>Đợt quái vật thứ hai Hoạt động 4010 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Nhận Thưởng Kinh Nghiệm Rương Vật Phẩm Phụ Bản 4010</t>
+          <t>Phần thưởng Kinh nghiệm Rương Cung Ứng Thử Thách 4010</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Instance 4020 Step 1 Completed</t>
+          <t>Hoàn thành Bước 1 - Thử Thách 4020</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Instance 4020 Step 2 Completed</t>
+          <t>Hoàn thành Bước 2 - Thử Thách 4020</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Instance 4020 Step 3 Completed</t>
+          <t>Hoàn thành Bước 3 - Thử Thách 4020</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Instance 4020 Step 4 Completed</t>
+          <t>Hoàn thành Bước 4 - Thử Thách 4020</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Instance 4020 Step 5 Completed</t>
+          <t>Hoàn thành Bước 5 - Thử Thách 4020</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Instance 4020 Step 6 Completed</t>
+          <t>Hoàn thành Bước 6 - Thử Thách 4020</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Nhất Phụ Bản 4020</t>
+          <t>Đã tiêu diệt Đợt Quái Vật đầu tiên - Thử Thách 4020</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Hai Phụ Bản 4020</t>
+          <t>Đã tiêu diệt Đợt Quái Vật thứ hai - Thử Thách 4020</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Tiêu diệt Đợt Quái Vật Thứ Hai Phụ Bản 4020</t>
+          <t>Đã tiêu diệt Đợt Quái Vật thứ hai - Thử Thách 4020</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Nhận Thưởng Kinh Nghiệm Rương Vật Phẩm Phụ Bản 4020</t>
+          <t>Phần thưởng Kinh nghiệm Rương Cung Ứng Thử Thách 4020</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Instance Points Acquired</t>
+          <t>Điểm Thể Hiện đã nhận</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Instance 4030 Step 1 Completed</t>
+          <t>Giai đoạn 1 Tổ 4030 hoàn thành</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Instance 4030 Step 2 Completed</t>
+          <t>Giai đoạn 2 Tổ 4030 hoàn thành</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Instance 4030 Step 3 Completed</t>
+          <t>Giai đoạn 3 Tổ 4030 hoàn thành</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Instance 4030 Step 4 Completed</t>
+          <t>Giai đoạn 4 Tổ 4030 hoàn thành</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Instance 4030 Step 5 Completed</t>
+          <t>Giai đoạn 5 Tổ 4030 hoàn thành</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Instance 4030 Step 6 Completed</t>
+          <t>Giai đoạn 6 Tổ 4030 hoàn thành</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật đầu tiên - Thể nghiệm 4030</t>
+          <t>Đã tiêu diệt Đợt Quái Vật đầu tiên - Thử Thách 4030</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ hai - Thể nghiệm 4030</t>
+          <t>Đã tiêu diệt Đợt Quái Vật thứ hai - Thử Thách 4030</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ hai - Thể nghiệm 4030</t>
+          <t>Đã tiêu diệt Đợt Quái Vật thứ hai - Thử Thách 4030</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Phần thưởng Kinh nghiệm Rương Cung ứng - Thể nghiệm 4030</t>
+          <t>Rương tiếp tế Tổ 4030 - Phần thưởng Kinh nghiệm</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Instance 4040 Step 1 Completed</t>
+          <t>Giai đoạn 1 Tổ 4040 hoàn thành</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Instance 4040 Step 2 Completed</t>
+          <t>Giai đoạn 2 Tổ 4040 hoàn thành</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Instance 4040 Step 3 Completed</t>
+          <t>Giai đoạn 3 Tổ 4040 hoàn thành</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Instance 4040 Step 4 Completed</t>
+          <t>Giai đoạn 4 Tổ 4040 hoàn thành</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Instance 4040 Step 5 Completed</t>
+          <t>Giai đoạn 5 Tổ 4040 hoàn thành</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Instance 4040 Step 6 Completed</t>
+          <t>Giai đoạn 6 Tổ 4040 hoàn thành</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật đầu tiên - Thể nghiệm 4040</t>
+          <t>Đợt quái vật đầu Tổ 4040 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ hai - Thể nghiệm 4040</t>
+          <t>Đợt quái vật thứ hai Tổ 4040 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ hai - Thể nghiệm 4040</t>
+          <t>Đợt quái vật thứ hai Tổ 4040 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Phần thưởng Kinh nghiệm Rương Cung ứng - Thể nghiệm 4040</t>
+          <t>Rương tiếp tế Tổ 4040 - Phần thưởng Kinh nghiệm</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Instance 4050 Step 1 Completed</t>
+          <t>Giai đoạn 1 Tổ 4050 hoàn thành</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Instance 4050 Step 2 Completed</t>
+          <t>Giai đoạn 2 Tổ 4050 hoàn thành</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Instance 4050 Step 3 Completed</t>
+          <t>Giai đoạn 3 Tổ 4050 hoàn thành</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Instance 4050 Step 4 Completed</t>
+          <t>Giai đoạn 4 Tổ 4050 hoàn thành</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Instance 4050 Step 5 Completed</t>
+          <t>Giai đoạn 5 Tổ 4050 hoàn thành</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Instance 4050 Step 6 Completed</t>
+          <t>Giai đoạn 6 Tổ 4050 hoàn thành</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật đầu tiên - Thể nghiệm 4050</t>
+          <t>Làn sóng quái vật đầu tiên Tổ 4050 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ hai - Thể nghiệm 4050</t>
+          <t>Làn sóng quái vật thứ hai Tổ 4050 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ hai - Thể nghiệm 4050</t>
+          <t>Làn sóng quái vật thứ hai Tổ 4050 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Phần thưởng Kinh nghiệm Rương Cung ứng - Thể nghiệm 4050</t>
+          <t>Phần thưởng Kinh nghiệm Rương Cung Cấp Thể Hiện 4050</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 1 Completed</t>
+          <t>Instance 170000100 Bước 1 hoàn thành</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 2 Completed</t>
+          <t>Giai đoạn 2 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 3 Completed</t>
+          <t>Giai đoạn 3 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 4 Completed</t>
+          <t>Thao tác 170000100 Bước 4 hoàn tất</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 5 Completed</t>
+          <t>Giai đoạn 5 - Tổ Tacet 170000100 hoàn thành</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 6 Completed</t>
+          <t>Giai đoạn 6 - Tổ Tacet 170000100 hoàn thành</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 7 Completed</t>
+          <t>Giai đoạn 7 - Tổ Tacet 170000100 hoàn thành</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 8 Completed</t>
+          <t>Giai đoạn 8 - Tổ Tacet 170000100 hoàn thành</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 9 Completed</t>
+          <t>Giai đoạn 9 - Tổ Tacet 170000100 hoàn thành</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 10 Completed</t>
+          <t>Instance 170000100 Bước 10 hoàn thành</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 11 Completed</t>
+          <t>Instance 170000100 Bước 11 hoàn thành</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 12 Completed</t>
+          <t>Instance 170000100 Bước 12 hoàn thành</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 13 Completed</t>
+          <t>Instance 170000100 Bước 13 hoàn thành</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 14 Completed</t>
+          <t>Instance 170000100 Bước 14 hoàn thành</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 15 Completed</t>
+          <t>Instance 170000100 Bước 15 hoàn thành</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 16 Completed</t>
+          <t>Instance 170000100 Bước 16 hoàn thành</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 17 Completed</t>
+          <t>Instance 170000100 Bước 17 hoàn thành</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 18 Completed</t>
+          <t>Instance 170000100 Bước 18 hoàn thành</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 19 Completed</t>
+          <t>Instance 170000100 Bước 19 hoàn thành</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 20 Completed</t>
+          <t>Giai đoạn 20 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 21 Completed</t>
+          <t>Giai đoạn 21 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 22 Completed</t>
+          <t>Giai đoạn 22 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 23 Completed</t>
+          <t>Giai đoạn 23 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 24 Completed</t>
+          <t>Giai đoạn 24 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 25 Completed</t>
+          <t>Giai đoạn 25 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 26 Completed</t>
+          <t>Giai đoạn 26 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 27 Completed</t>
+          <t>Giai đoạn 27 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 28 Completed</t>
+          <t>Giai đoạn 28 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 29 Completed</t>
+          <t>Giai đoạn 29 Hoàn thành - Tổ Tacet 170000100</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 30 Completed</t>
+          <t>Thao tác 170000100 Bước 30 hoàn tất</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 31 Completed</t>
+          <t>Thao tác 170000100 Bước 31 hoàn tất</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 32 Completed</t>
+          <t>Thao tác 170000100 Bước 32 hoàn tất</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 33 Completed</t>
+          <t>Thao tác 170000100 Bước 33 hoàn tất</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 34 Completed</t>
+          <t>Thao tác 170000100 Bước 34 hoàn tất</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 35 Completed</t>
+          <t>Thao tác 170000100 Bước 35 hoàn tất</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 36 Completed</t>
+          <t>Thao tác 170000100 Bước 36 hoàn tất</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 37 Completed</t>
+          <t>Thao tác 170000100 Bước 37 hoàn tất</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 38 Completed</t>
+          <t>Thao tác 170000100 Bước 38 hoàn tất</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 39 Completed</t>
+          <t>Thao tác 170000100 Bước 39 hoàn tất</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật đầu tiên - Thể nghiệm 170000100</t>
+          <t>Làn sóng quái vật đầu tiên đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ hai - Thể nghiệm 170000100</t>
+          <t>Làn sóng quái vật thứ hai đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ ba - Thể nghiệm 170000100</t>
+          <t>Làn sóng quái vật thứ ba đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ tư - Thể nghiệm 170000100</t>
+          <t>Làn sóng quái vật thứ tư đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ năm - Thể nghiệm 170000100</t>
+          <t>Làn sóng quái vật thứ năm đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ sáu - Thể nghiệm 170000100</t>
+          <t>Làn sóng quái vật thứ sáu đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ bảy - Thể nghiệm 170000100</t>
+          <t>Làn sóng quái vật thứ bảy đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ tám - Thể nghiệm 170000100</t>
+          <t>Làn sóng quái vật thứ tám đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ chín - Thể nghiệm 170000100</t>
+          <t>Instance 170000100 Đợt quái vật thứ 9 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ mười - Thể nghiệm 170000100</t>
+          <t>Phó bản 170000100 - Đợt quái vật thứ 10 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ mười một - Thể nghiệm 170000100</t>
+          <t>Phó bản 170000100 - Đợt quái vật thứ 11 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ mười hai - Thể nghiệm 170000100</t>
+          <t>Phó bản 170000100 - Đợt quái vật thứ 12 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ mười ba - Thể nghiệm 170000100</t>
+          <t>Phó bản 170000100 - Đợt quái vật thứ 13 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Đợt Quái Vật Thứ 14 Trong Phòng Thử Thách 170000100 Bị Tiêu Diệt</t>
+          <t>Phó bản 170000100 - Đợt quái vật thứ 14 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Đợt Quái Vật Thứ 15 Trong Phòng Thử Thách 170000100 Bị Tiêu Diệt</t>
+          <t>Phó bản 170000100 - Đợt quái vật thứ 15 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Đợt Quái Vật Thứ 16 Trong Phòng Thử Thách 170000100 Bị Tiêu Diệt</t>
+          <t>Phó bản 170000100 - Đợt quái vật thứ 16 bị tiêu diệt</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Đợt Quái Vật Thứ 17 Trong Phòng Thử Thách 170000100 Bị Tiêu Diệt</t>
+          <t>Làn sóng quái vật thứ 17 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Đợt Quái Vật Thứ 18 Trong Phòng Thử Thách 170000100 Bị Tiêu Diệt</t>
+          <t>Làn sóng quái vật thứ 18 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Đợt Quái Vật Thứ 19 Trong Phòng Thử Thách 170000100 Bị Tiêu Diệt</t>
+          <t>Làn sóng quái vật thứ 19 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Đợt Quái Vật Thứ 20 Trong Phòng Thử Thách 170000100 Bị Tiêu Diệt</t>
+          <t>Làn sóng quái vật thứ 20 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 40 Completed</t>
+          <t>Thao tác 170000100 Bước 40 hoàn tất</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 41 Completed</t>
+          <t>Giai đoạn 41 - Tổ Tacet 170000100 hoàn thành</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Instance 170000100 Step 42 Completed</t>
+          <t>Giai đoạn 42 - Tổ Tacet 170000100 hoàn thành</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Mở Rương Cung Ứng Trong Phòng Thử Thách Vực Sâu</t>
+          <t>Rương Cung Ứng Vực Sâu đã mở</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Instance 6000 Step 1 Completed</t>
+          <t>Bước 1 của Thể Hiện 6000 hoàn thành</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Instance 6000 Step 2 Completed</t>
+          <t>Bước 2 của Thể Hiện 6000 hoàn thành</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Instance 6000 Step 3 Completed</t>
+          <t>Bước 3 của Thể Hiện 6000 hoàn thành</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Instance 6000 Step 4 Completed</t>
+          <t>Bước 4 của Thể Hiện 6000 hoàn thành</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Instance 6000 Step 5 Completed</t>
+          <t>Bước 5 của Thể Hiện 6000 hoàn thành</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Instance 6000 Step 6 Completed</t>
+          <t>Bước 6 của Thể Hiện 6000 hoàn thành</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Đợt Quái Vật Thứ 1 Trong Phòng Thử Thách 6000 Bị Tiêu Diệt</t>
+          <t>Đợt quái vật đầu tiên của Thể Hiện 6000 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Đợt Quái Vật Thứ 2 Trong Phòng Thử Thách 6000 Bị Tiêu Diệt</t>
+          <t>Đợt quái thứ hai của Thể Hiện 6000 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Đợt Quái Vật Thứ 3 Trong Phòng Thử Thách 6000 Bị Tiêu Diệt</t>
+          <t>Đợt quái thứ ba của Thể Hiện 6000 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Vực Sâu I - Đợt Tiêu Diệt Quái Vật I</t>
+          <t>Đợt Tiễu Trừ Quái Vực Sâu I - Giai Đoạn I</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Vực Sâu I - Đợt Tiêu Diệt Quái Vật II</t>
+          <t>Đợt Tiễu Trừ Quái Vực Sâu I - Giai Đoạn II</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Vực Sâu I - Đợt Tiêu Diệt Quái Vật III</t>
+          <t>Đợt Tiễu Trừ Quái Vực Sâu I - Giai Đoạn III</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Vực Sâu II - Đợt Tiêu Diệt Quái Vật I</t>
+          <t>Đợt Tiễu Trừ Quái Vực Sâu II - Giai Đoạn I</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Vực Sâu II - Đợt Tiêu Diệt Quái Vật II</t>
+          <t>Đợt Tiễu Trừ Quái Vực Sâu II - Giai Đoạn II</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Vực Sâu II - Đợt Tiêu Diệt Quái Vật III</t>
+          <t>Đợt III - Sát Quái Vực Sâu II</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Vực Sâu III - Đợt Tiêu Diệt Quái Vật I</t>
+          <t>Đợt I - Sát Quái Vực Sâu III</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
